--- a/artfynd/A 38443-2021 artfynd.xlsx
+++ b/artfynd/A 38443-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38443-2021 artfynd.xlsx
+++ b/artfynd/A 38443-2021 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>96878747</v>
       </c>
       <c r="B2" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752290.0656550771</v>
+        <v>752290</v>
       </c>
       <c r="R2" t="n">
-        <v>7088236.660969114</v>
+        <v>7088237</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-10-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96878748</v>
+        <v>96878750</v>
       </c>
       <c r="B3" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752290.0656550771</v>
+        <v>752322</v>
       </c>
       <c r="R3" t="n">
-        <v>7088236.660969114</v>
+        <v>7088229</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2021-10-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96878749</v>
+        <v>96878748</v>
       </c>
       <c r="B4" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752329.109560509</v>
+        <v>752290</v>
       </c>
       <c r="R4" t="n">
-        <v>7088220.304760726</v>
+        <v>7088237</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2021-10-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96878750</v>
+        <v>96878749</v>
       </c>
       <c r="B5" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>752322.1905999436</v>
+        <v>752329</v>
       </c>
       <c r="R5" t="n">
-        <v>7088229.055355716</v>
+        <v>7088220</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2021-10-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-10-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,12 +1066,7 @@
         <v>119303924</v>
       </c>
       <c r="B6" t="n">
-        <v>91863</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
